--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210195</v>
+        <v>113210221</v>
       </c>
       <c r="B6" t="n">
-        <v>56765</v>
+        <v>79169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543458</v>
+        <v>543400</v>
       </c>
       <c r="R6" t="n">
-        <v>7204009</v>
+        <v>7204030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210270</v>
+        <v>113210267</v>
       </c>
       <c r="B7" t="n">
         <v>78105</v>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543369</v>
+        <v>543370</v>
       </c>
       <c r="R7" t="n">
-        <v>7204270</v>
+        <v>7204023</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210221</v>
+        <v>113210270</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>78105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543400</v>
+        <v>543369</v>
       </c>
       <c r="R9" t="n">
-        <v>7204030</v>
+        <v>7204270</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210267</v>
+        <v>113210195</v>
       </c>
       <c r="B10" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543370</v>
+        <v>543458</v>
       </c>
       <c r="R10" t="n">
-        <v>7204023</v>
+        <v>7204009</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2034,7 +2034,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210277</v>
+        <v>113210265</v>
       </c>
       <c r="B14" t="n">
         <v>78105</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543441</v>
+        <v>543457</v>
       </c>
       <c r="R14" t="n">
-        <v>7204521</v>
+        <v>7204023</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210265</v>
+        <v>113210206</v>
       </c>
       <c r="B15" t="n">
-        <v>78105</v>
+        <v>79195</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543457</v>
+        <v>543426</v>
       </c>
       <c r="R15" t="n">
-        <v>7204023</v>
+        <v>7204342</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210206</v>
+        <v>113210277</v>
       </c>
       <c r="B16" t="n">
-        <v>79195</v>
+        <v>78105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2270,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543426</v>
+        <v>543441</v>
       </c>
       <c r="R16" t="n">
-        <v>7204342</v>
+        <v>7204521</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210222</v>
+        <v>113210194</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>56765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543338</v>
+        <v>543464</v>
       </c>
       <c r="R2" t="n">
-        <v>7204158</v>
+        <v>7204006</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210188</v>
+        <v>113210269</v>
       </c>
       <c r="B3" t="n">
-        <v>74286</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543416</v>
+        <v>543356</v>
       </c>
       <c r="R3" t="n">
-        <v>7204379</v>
+        <v>7204196</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210274</v>
+        <v>113210277</v>
       </c>
       <c r="B4" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543417</v>
+        <v>543441</v>
       </c>
       <c r="R4" t="n">
-        <v>7204383</v>
+        <v>7204521</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210220</v>
+        <v>113210274</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543501</v>
+        <v>543417</v>
       </c>
       <c r="R5" t="n">
-        <v>7203965</v>
+        <v>7204383</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210221</v>
+        <v>113210222</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543400</v>
+        <v>543338</v>
       </c>
       <c r="R6" t="n">
-        <v>7204030</v>
+        <v>7204158</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210267</v>
+        <v>113210266</v>
       </c>
       <c r="B7" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543370</v>
+        <v>543399</v>
       </c>
       <c r="R7" t="n">
-        <v>7204023</v>
+        <v>7204037</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210199</v>
+        <v>113210223</v>
       </c>
       <c r="B8" t="n">
-        <v>56765</v>
+        <v>79118</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,43 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543356</v>
+        <v>543414</v>
       </c>
       <c r="R8" t="n">
-        <v>7204193</v>
+        <v>7204395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210270</v>
+        <v>113210239</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>90063</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543369</v>
+        <v>543380</v>
       </c>
       <c r="R9" t="n">
-        <v>7204270</v>
+        <v>7204272</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210195</v>
+        <v>113210186</v>
       </c>
       <c r="B10" t="n">
-        <v>56765</v>
+        <v>74302</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543458</v>
+        <v>543457</v>
       </c>
       <c r="R10" t="n">
-        <v>7204009</v>
+        <v>7204024</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210272</v>
+        <v>113210195</v>
       </c>
       <c r="B11" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,34 +1704,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543381</v>
+        <v>543458</v>
       </c>
       <c r="R11" t="n">
-        <v>7204285</v>
+        <v>7204009</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210201</v>
+        <v>113210271</v>
       </c>
       <c r="B12" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543371</v>
+        <v>543369</v>
       </c>
       <c r="R12" t="n">
-        <v>7204278</v>
+        <v>7204284</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1922,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210262</v>
+        <v>113210232</v>
       </c>
       <c r="B13" t="n">
-        <v>78105</v>
+        <v>79218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543464</v>
+        <v>543400</v>
       </c>
       <c r="R13" t="n">
-        <v>7203981</v>
+        <v>7204030</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210265</v>
+        <v>113210229</v>
       </c>
       <c r="B14" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543457</v>
+        <v>543341</v>
       </c>
       <c r="R14" t="n">
-        <v>7204023</v>
+        <v>7204156</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210206</v>
+        <v>113210200</v>
       </c>
       <c r="B15" t="n">
-        <v>79195</v>
+        <v>56765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,38 +2153,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543426</v>
+        <v>543369</v>
       </c>
       <c r="R15" t="n">
-        <v>7204342</v>
+        <v>7204270</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210277</v>
+        <v>113210221</v>
       </c>
       <c r="B16" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543441</v>
+        <v>543400</v>
       </c>
       <c r="R16" t="n">
-        <v>7204521</v>
+        <v>7204030</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210232</v>
+        <v>113210270</v>
       </c>
       <c r="B17" t="n">
-        <v>79202</v>
+        <v>78121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543400</v>
+        <v>543369</v>
       </c>
       <c r="R17" t="n">
-        <v>7204030</v>
+        <v>7204270</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210219</v>
+        <v>113210275</v>
       </c>
       <c r="B18" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543507</v>
+        <v>543411</v>
       </c>
       <c r="R18" t="n">
-        <v>7203943</v>
+        <v>7204394</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210273</v>
+        <v>113210268</v>
       </c>
       <c r="B19" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543426</v>
+        <v>543344</v>
       </c>
       <c r="R19" t="n">
-        <v>7204339</v>
+        <v>7204178</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210234</v>
+        <v>113210220</v>
       </c>
       <c r="B20" t="n">
-        <v>77086</v>
+        <v>79185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543438</v>
+        <v>543501</v>
       </c>
       <c r="R20" t="n">
-        <v>7204529</v>
+        <v>7203965</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210268</v>
+        <v>113210198</v>
       </c>
       <c r="B21" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,34 +2834,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543344</v>
+        <v>543348</v>
       </c>
       <c r="R21" t="n">
-        <v>7204178</v>
+        <v>7204165</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210239</v>
+        <v>113210201</v>
       </c>
       <c r="B22" t="n">
-        <v>90047</v>
+        <v>56765</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,34 +2951,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543380</v>
+        <v>543371</v>
       </c>
       <c r="R22" t="n">
-        <v>7204272</v>
+        <v>7204278</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210196</v>
+        <v>113210262</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,39 +3068,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543372</v>
+        <v>543464</v>
       </c>
       <c r="R23" t="n">
-        <v>7204028</v>
+        <v>7203981</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210193</v>
+        <v>113210188</v>
       </c>
       <c r="B24" t="n">
-        <v>56765</v>
+        <v>74302</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,39 +3180,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543467</v>
+        <v>543416</v>
       </c>
       <c r="R24" t="n">
-        <v>7203980</v>
+        <v>7204379</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210198</v>
+        <v>113210234</v>
       </c>
       <c r="B25" t="n">
-        <v>56765</v>
+        <v>77102</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,39 +3292,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543348</v>
+        <v>543438</v>
       </c>
       <c r="R25" t="n">
-        <v>7204165</v>
+        <v>7204529</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,7 +3388,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210200</v>
+        <v>113210193</v>
       </c>
       <c r="B26" t="n">
         <v>56765</v>
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543369</v>
+        <v>543467</v>
       </c>
       <c r="R26" t="n">
-        <v>7204270</v>
+        <v>7203980</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3473,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210261</v>
+        <v>113210264</v>
       </c>
       <c r="B27" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543502</v>
+        <v>543460</v>
       </c>
       <c r="R27" t="n">
-        <v>7203971</v>
+        <v>7204008</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3585,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3622,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210266</v>
+        <v>113210196</v>
       </c>
       <c r="B28" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3638,34 +3633,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543399</v>
+        <v>543372</v>
       </c>
       <c r="R28" t="n">
-        <v>7204037</v>
+        <v>7204028</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210263</v>
+        <v>113210267</v>
       </c>
       <c r="B29" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543461</v>
+        <v>543370</v>
       </c>
       <c r="R29" t="n">
-        <v>7204010</v>
+        <v>7204023</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210229</v>
+        <v>113210265</v>
       </c>
       <c r="B30" t="n">
-        <v>79168</v>
+        <v>78121</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543341</v>
+        <v>543457</v>
       </c>
       <c r="R30" t="n">
-        <v>7204156</v>
+        <v>7204023</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210264</v>
+        <v>113210273</v>
       </c>
       <c r="B31" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543460</v>
+        <v>543426</v>
       </c>
       <c r="R31" t="n">
-        <v>7204008</v>
+        <v>7204339</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210187</v>
+        <v>113210272</v>
       </c>
       <c r="B32" t="n">
-        <v>74286</v>
+        <v>78121</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,21 +4086,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543382</v>
+        <v>543381</v>
       </c>
       <c r="R32" t="n">
-        <v>7204281</v>
+        <v>7204285</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210275</v>
+        <v>113210259</v>
       </c>
       <c r="B33" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543411</v>
+        <v>543507</v>
       </c>
       <c r="R33" t="n">
-        <v>7204394</v>
+        <v>7203943</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210223</v>
+        <v>113210187</v>
       </c>
       <c r="B34" t="n">
-        <v>79102</v>
+        <v>74302</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4306,25 +4306,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543414</v>
+        <v>543382</v>
       </c>
       <c r="R34" t="n">
-        <v>7204395</v>
+        <v>7204281</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210259</v>
+        <v>113210206</v>
       </c>
       <c r="B35" t="n">
-        <v>78105</v>
+        <v>79211</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,25 +4418,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543507</v>
+        <v>543426</v>
       </c>
       <c r="R35" t="n">
-        <v>7203943</v>
+        <v>7204342</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210269</v>
+        <v>113210199</v>
       </c>
       <c r="B36" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,24 +4534,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
@@ -4561,7 +4566,7 @@
         <v>543356</v>
       </c>
       <c r="R36" t="n">
-        <v>7204196</v>
+        <v>7204193</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4630,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210194</v>
+        <v>113210219</v>
       </c>
       <c r="B37" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,39 +4651,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543464</v>
+        <v>543507</v>
       </c>
       <c r="R37" t="n">
-        <v>7204006</v>
+        <v>7203943</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210271</v>
+        <v>113210261</v>
       </c>
       <c r="B38" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543369</v>
+        <v>543502</v>
       </c>
       <c r="R38" t="n">
-        <v>7204284</v>
+        <v>7203971</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210186</v>
+        <v>113210263</v>
       </c>
       <c r="B39" t="n">
-        <v>74286</v>
+        <v>78121</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543457</v>
+        <v>543461</v>
       </c>
       <c r="R39" t="n">
-        <v>7204024</v>
+        <v>7204010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210222</v>
+        <v>113210223</v>
       </c>
       <c r="B6" t="n">
-        <v>79185</v>
+        <v>79118</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543338</v>
+        <v>543414</v>
       </c>
       <c r="R6" t="n">
-        <v>7204158</v>
+        <v>7204395</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210266</v>
+        <v>113210222</v>
       </c>
       <c r="B7" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543399</v>
+        <v>543338</v>
       </c>
       <c r="R7" t="n">
-        <v>7204037</v>
+        <v>7204158</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210223</v>
+        <v>113210239</v>
       </c>
       <c r="B8" t="n">
-        <v>79118</v>
+        <v>90063</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543414</v>
+        <v>543380</v>
       </c>
       <c r="R8" t="n">
-        <v>7204395</v>
+        <v>7204272</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210239</v>
+        <v>113210266</v>
       </c>
       <c r="B9" t="n">
-        <v>90063</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543380</v>
+        <v>543399</v>
       </c>
       <c r="R9" t="n">
-        <v>7204272</v>
+        <v>7204037</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210220</v>
+        <v>113210262</v>
       </c>
       <c r="B20" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543501</v>
+        <v>543464</v>
       </c>
       <c r="R20" t="n">
-        <v>7203965</v>
+        <v>7203981</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210198</v>
+        <v>113210188</v>
       </c>
       <c r="B21" t="n">
-        <v>56765</v>
+        <v>74302</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,39 +2834,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543348</v>
+        <v>543416</v>
       </c>
       <c r="R21" t="n">
-        <v>7204165</v>
+        <v>7204379</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210201</v>
+        <v>113210198</v>
       </c>
       <c r="B22" t="n">
         <v>56765</v>
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543371</v>
+        <v>543348</v>
       </c>
       <c r="R22" t="n">
-        <v>7204278</v>
+        <v>7204165</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210262</v>
+        <v>113210201</v>
       </c>
       <c r="B23" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,34 +3063,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543464</v>
+        <v>543371</v>
       </c>
       <c r="R23" t="n">
-        <v>7203981</v>
+        <v>7204278</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210188</v>
+        <v>113210220</v>
       </c>
       <c r="B24" t="n">
-        <v>74302</v>
+        <v>79185</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543416</v>
+        <v>543501</v>
       </c>
       <c r="R24" t="n">
-        <v>7204379</v>
+        <v>7203965</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210234</v>
+        <v>113210264</v>
       </c>
       <c r="B25" t="n">
-        <v>77102</v>
+        <v>78121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,21 +3292,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543438</v>
+        <v>543460</v>
       </c>
       <c r="R25" t="n">
-        <v>7204529</v>
+        <v>7204008</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210264</v>
+        <v>113210234</v>
       </c>
       <c r="B27" t="n">
-        <v>78121</v>
+        <v>77102</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,21 +3521,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543460</v>
+        <v>543438</v>
       </c>
       <c r="R27" t="n">
-        <v>7204008</v>
+        <v>7204529</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210196</v>
+        <v>113210267</v>
       </c>
       <c r="B28" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,39 +3633,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543372</v>
+        <v>543370</v>
       </c>
       <c r="R28" t="n">
-        <v>7204028</v>
+        <v>7204023</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3734,7 +3729,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210267</v>
+        <v>113210265</v>
       </c>
       <c r="B29" t="n">
         <v>78121</v>
@@ -3774,7 +3769,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543370</v>
+        <v>543457</v>
       </c>
       <c r="R29" t="n">
         <v>7204023</v>
@@ -3809,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210265</v>
+        <v>113210196</v>
       </c>
       <c r="B30" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,34 +3857,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543457</v>
+        <v>543372</v>
       </c>
       <c r="R30" t="n">
-        <v>7204023</v>
+        <v>7204028</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210259</v>
+        <v>113210199</v>
       </c>
       <c r="B33" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,34 +4198,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543507</v>
+        <v>543356</v>
       </c>
       <c r="R33" t="n">
-        <v>7203943</v>
+        <v>7204193</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210187</v>
+        <v>113210259</v>
       </c>
       <c r="B34" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,21 +4315,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,10 +4339,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543382</v>
+        <v>543507</v>
       </c>
       <c r="R34" t="n">
-        <v>7204281</v>
+        <v>7203943</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,10 +4411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210206</v>
+        <v>113210187</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>74302</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,25 +4423,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4446,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543426</v>
+        <v>543382</v>
       </c>
       <c r="R35" t="n">
-        <v>7204342</v>
+        <v>7204281</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210199</v>
+        <v>113210206</v>
       </c>
       <c r="B36" t="n">
-        <v>56765</v>
+        <v>79211</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4530,43 +4535,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543356</v>
+        <v>543426</v>
       </c>
       <c r="R36" t="n">
-        <v>7204193</v>
+        <v>7204342</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210219</v>
+        <v>113210261</v>
       </c>
       <c r="B37" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543507</v>
+        <v>543502</v>
       </c>
       <c r="R37" t="n">
-        <v>7203943</v>
+        <v>7203971</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,7 +4747,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210261</v>
+        <v>113210263</v>
       </c>
       <c r="B38" t="n">
         <v>78121</v>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543502</v>
+        <v>543461</v>
       </c>
       <c r="R38" t="n">
-        <v>7203971</v>
+        <v>7204010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210263</v>
+        <v>113210219</v>
       </c>
       <c r="B39" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543461</v>
+        <v>543507</v>
       </c>
       <c r="R39" t="n">
-        <v>7204010</v>
+        <v>7203943</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210194</v>
+        <v>113210223</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>79118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543464</v>
+        <v>543414</v>
       </c>
       <c r="R2" t="n">
-        <v>7204006</v>
+        <v>7204395</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210269</v>
+        <v>113210277</v>
       </c>
       <c r="B3" t="n">
         <v>78121</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543356</v>
+        <v>543441</v>
       </c>
       <c r="R3" t="n">
-        <v>7204196</v>
+        <v>7204521</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210277</v>
+        <v>113210271</v>
       </c>
       <c r="B4" t="n">
         <v>78121</v>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543441</v>
+        <v>543369</v>
       </c>
       <c r="R4" t="n">
-        <v>7204521</v>
+        <v>7204284</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210274</v>
+        <v>113210265</v>
       </c>
       <c r="B5" t="n">
         <v>78121</v>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543417</v>
+        <v>543457</v>
       </c>
       <c r="R5" t="n">
-        <v>7204383</v>
+        <v>7204023</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210223</v>
+        <v>113210272</v>
       </c>
       <c r="B6" t="n">
-        <v>79118</v>
+        <v>78121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543414</v>
+        <v>543381</v>
       </c>
       <c r="R6" t="n">
-        <v>7204395</v>
+        <v>7204285</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210222</v>
+        <v>113210196</v>
       </c>
       <c r="B7" t="n">
-        <v>79185</v>
+        <v>56765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1251,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543338</v>
+        <v>543372</v>
       </c>
       <c r="R7" t="n">
-        <v>7204158</v>
+        <v>7204028</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210239</v>
+        <v>113210273</v>
       </c>
       <c r="B8" t="n">
-        <v>90063</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543380</v>
+        <v>543426</v>
       </c>
       <c r="R8" t="n">
-        <v>7204272</v>
+        <v>7204339</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210266</v>
+        <v>113210268</v>
       </c>
       <c r="B9" t="n">
         <v>78121</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543399</v>
+        <v>543344</v>
       </c>
       <c r="R9" t="n">
-        <v>7204037</v>
+        <v>7204178</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210186</v>
+        <v>113210274</v>
       </c>
       <c r="B10" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543457</v>
+        <v>543417</v>
       </c>
       <c r="R10" t="n">
-        <v>7204024</v>
+        <v>7204383</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210195</v>
+        <v>113210198</v>
       </c>
       <c r="B11" t="n">
         <v>56765</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543458</v>
+        <v>543348</v>
       </c>
       <c r="R11" t="n">
-        <v>7204009</v>
+        <v>7204165</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210271</v>
+        <v>113210219</v>
       </c>
       <c r="B12" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543369</v>
+        <v>543507</v>
       </c>
       <c r="R12" t="n">
-        <v>7204284</v>
+        <v>7203943</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210232</v>
+        <v>113210269</v>
       </c>
       <c r="B13" t="n">
-        <v>79218</v>
+        <v>78121</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543400</v>
+        <v>543356</v>
       </c>
       <c r="R13" t="n">
-        <v>7204030</v>
+        <v>7204196</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210229</v>
+        <v>113210234</v>
       </c>
       <c r="B14" t="n">
-        <v>79184</v>
+        <v>77102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543341</v>
+        <v>543438</v>
       </c>
       <c r="R14" t="n">
-        <v>7204156</v>
+        <v>7204529</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210200</v>
+        <v>113210222</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,39 +2157,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543369</v>
+        <v>543338</v>
       </c>
       <c r="R15" t="n">
-        <v>7204270</v>
+        <v>7204158</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210221</v>
+        <v>113210206</v>
       </c>
       <c r="B16" t="n">
-        <v>79185</v>
+        <v>79211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2265,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543400</v>
+        <v>543426</v>
       </c>
       <c r="R16" t="n">
-        <v>7204030</v>
+        <v>7204342</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2365,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210270</v>
+        <v>113210267</v>
       </c>
       <c r="B17" t="n">
         <v>78121</v>
@@ -2410,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543369</v>
+        <v>543370</v>
       </c>
       <c r="R17" t="n">
-        <v>7204270</v>
+        <v>7204023</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210275</v>
+        <v>113210199</v>
       </c>
       <c r="B18" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,34 +2493,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543411</v>
+        <v>543356</v>
       </c>
       <c r="R18" t="n">
-        <v>7204394</v>
+        <v>7204193</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210268</v>
+        <v>113210187</v>
       </c>
       <c r="B19" t="n">
-        <v>78121</v>
+        <v>74302</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543344</v>
+        <v>543382</v>
       </c>
       <c r="R19" t="n">
-        <v>7204178</v>
+        <v>7204281</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210262</v>
+        <v>113210221</v>
       </c>
       <c r="B20" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543464</v>
+        <v>543400</v>
       </c>
       <c r="R20" t="n">
-        <v>7203981</v>
+        <v>7204030</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210188</v>
+        <v>113210275</v>
       </c>
       <c r="B21" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543416</v>
+        <v>543411</v>
       </c>
       <c r="R21" t="n">
-        <v>7204379</v>
+        <v>7204394</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210198</v>
+        <v>113210195</v>
       </c>
       <c r="B22" t="n">
         <v>56765</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543348</v>
+        <v>543458</v>
       </c>
       <c r="R22" t="n">
-        <v>7204165</v>
+        <v>7204009</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210201</v>
+        <v>113210266</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,39 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543371</v>
+        <v>543399</v>
       </c>
       <c r="R23" t="n">
-        <v>7204278</v>
+        <v>7204037</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210220</v>
+        <v>113210200</v>
       </c>
       <c r="B24" t="n">
-        <v>79185</v>
+        <v>56765</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,34 +3175,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543501</v>
+        <v>543369</v>
       </c>
       <c r="R24" t="n">
-        <v>7203965</v>
+        <v>7204270</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210264</v>
+        <v>113210194</v>
       </c>
       <c r="B25" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,34 +3292,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543460</v>
+        <v>543464</v>
       </c>
       <c r="R25" t="n">
-        <v>7204008</v>
+        <v>7204006</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210234</v>
+        <v>113210229</v>
       </c>
       <c r="B27" t="n">
-        <v>77102</v>
+        <v>79184</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3521,21 +3526,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543438</v>
+        <v>543341</v>
       </c>
       <c r="R27" t="n">
-        <v>7204529</v>
+        <v>7204156</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3580,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,7 +3622,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210267</v>
+        <v>113210264</v>
       </c>
       <c r="B28" t="n">
         <v>78121</v>
@@ -3657,10 +3662,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543370</v>
+        <v>543460</v>
       </c>
       <c r="R28" t="n">
-        <v>7204023</v>
+        <v>7204008</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3692,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,7 +3734,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210265</v>
+        <v>113210262</v>
       </c>
       <c r="B29" t="n">
         <v>78121</v>
@@ -3769,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543457</v>
+        <v>543464</v>
       </c>
       <c r="R29" t="n">
-        <v>7204023</v>
+        <v>7203981</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210196</v>
+        <v>113210220</v>
       </c>
       <c r="B30" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,39 +3862,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543372</v>
+        <v>543501</v>
       </c>
       <c r="R30" t="n">
-        <v>7204028</v>
+        <v>7203965</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,7 +3958,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210273</v>
+        <v>113210261</v>
       </c>
       <c r="B31" t="n">
         <v>78121</v>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543426</v>
+        <v>543502</v>
       </c>
       <c r="R31" t="n">
-        <v>7204339</v>
+        <v>7203971</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210272</v>
+        <v>113210270</v>
       </c>
       <c r="B32" t="n">
         <v>78121</v>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543381</v>
+        <v>543369</v>
       </c>
       <c r="R32" t="n">
-        <v>7204285</v>
+        <v>7204270</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210199</v>
+        <v>113210201</v>
       </c>
       <c r="B33" t="n">
         <v>56765</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543356</v>
+        <v>543371</v>
       </c>
       <c r="R33" t="n">
-        <v>7204193</v>
+        <v>7204278</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,10 +4299,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210259</v>
+        <v>113210232</v>
       </c>
       <c r="B34" t="n">
-        <v>78121</v>
+        <v>79218</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,25 +4311,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543507</v>
+        <v>543400</v>
       </c>
       <c r="R34" t="n">
-        <v>7203943</v>
+        <v>7204030</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,7 +4411,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210187</v>
+        <v>113210188</v>
       </c>
       <c r="B35" t="n">
         <v>74302</v>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543382</v>
+        <v>543416</v>
       </c>
       <c r="R35" t="n">
-        <v>7204281</v>
+        <v>7204379</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210206</v>
+        <v>113210186</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>74302</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4535,25 +4535,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543426</v>
+        <v>543457</v>
       </c>
       <c r="R36" t="n">
-        <v>7204342</v>
+        <v>7204024</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210261</v>
+        <v>113210239</v>
       </c>
       <c r="B37" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543502</v>
+        <v>543380</v>
       </c>
       <c r="R37" t="n">
-        <v>7203971</v>
+        <v>7204272</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,7 +4747,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210263</v>
+        <v>113210259</v>
       </c>
       <c r="B38" t="n">
         <v>78121</v>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543461</v>
+        <v>543507</v>
       </c>
       <c r="R38" t="n">
-        <v>7204010</v>
+        <v>7203943</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210219</v>
+        <v>113210263</v>
       </c>
       <c r="B39" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543507</v>
+        <v>543461</v>
       </c>
       <c r="R39" t="n">
-        <v>7203943</v>
+        <v>7204010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210223</v>
+        <v>113210273</v>
       </c>
       <c r="B2" t="n">
-        <v>79118</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543414</v>
+        <v>543426</v>
       </c>
       <c r="R2" t="n">
-        <v>7204395</v>
+        <v>7204339</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210277</v>
+        <v>113210201</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543441</v>
+        <v>543371</v>
       </c>
       <c r="R3" t="n">
-        <v>7204521</v>
+        <v>7204278</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210271</v>
+        <v>113210270</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,7 +947,7 @@
         <v>543369</v>
       </c>
       <c r="R4" t="n">
-        <v>7204284</v>
+        <v>7204270</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210265</v>
+        <v>113210272</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543457</v>
+        <v>543381</v>
       </c>
       <c r="R5" t="n">
-        <v>7204023</v>
+        <v>7204285</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210272</v>
+        <v>113210198</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543381</v>
+        <v>543348</v>
       </c>
       <c r="R6" t="n">
-        <v>7204285</v>
+        <v>7204165</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210196</v>
+        <v>113210266</v>
       </c>
       <c r="B7" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543372</v>
+        <v>543399</v>
       </c>
       <c r="R7" t="n">
-        <v>7204028</v>
+        <v>7204037</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210273</v>
+        <v>113210199</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543426</v>
+        <v>543356</v>
       </c>
       <c r="R8" t="n">
-        <v>7204339</v>
+        <v>7204193</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210268</v>
+        <v>113210239</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>90075</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543344</v>
+        <v>543380</v>
       </c>
       <c r="R9" t="n">
-        <v>7204178</v>
+        <v>7204272</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210274</v>
+        <v>113210187</v>
       </c>
       <c r="B10" t="n">
-        <v>78121</v>
+        <v>74314</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543417</v>
+        <v>543382</v>
       </c>
       <c r="R10" t="n">
-        <v>7204383</v>
+        <v>7204281</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210198</v>
+        <v>113210186</v>
       </c>
       <c r="B11" t="n">
-        <v>56765</v>
+        <v>74314</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543348</v>
+        <v>543457</v>
       </c>
       <c r="R11" t="n">
-        <v>7204165</v>
+        <v>7204024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210219</v>
+        <v>113210263</v>
       </c>
       <c r="B12" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543507</v>
+        <v>543461</v>
       </c>
       <c r="R12" t="n">
-        <v>7203943</v>
+        <v>7204010</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210269</v>
+        <v>113210265</v>
       </c>
       <c r="B13" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543356</v>
+        <v>543457</v>
       </c>
       <c r="R13" t="n">
-        <v>7204196</v>
+        <v>7204023</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210234</v>
+        <v>113210262</v>
       </c>
       <c r="B14" t="n">
-        <v>77102</v>
+        <v>78133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543438</v>
+        <v>543464</v>
       </c>
       <c r="R14" t="n">
-        <v>7204529</v>
+        <v>7203981</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210222</v>
+        <v>113210277</v>
       </c>
       <c r="B15" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543338</v>
+        <v>543441</v>
       </c>
       <c r="R15" t="n">
-        <v>7204158</v>
+        <v>7204521</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210206</v>
+        <v>113210188</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>74314</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,25 +2270,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543426</v>
+        <v>543416</v>
       </c>
       <c r="R16" t="n">
-        <v>7204342</v>
+        <v>7204379</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210267</v>
+        <v>113210259</v>
       </c>
       <c r="B17" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543370</v>
+        <v>543507</v>
       </c>
       <c r="R17" t="n">
-        <v>7204023</v>
+        <v>7203943</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210199</v>
+        <v>113210268</v>
       </c>
       <c r="B18" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,39 +2498,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543356</v>
+        <v>543344</v>
       </c>
       <c r="R18" t="n">
-        <v>7204193</v>
+        <v>7204178</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210187</v>
+        <v>113210229</v>
       </c>
       <c r="B19" t="n">
-        <v>74302</v>
+        <v>79196</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543382</v>
+        <v>543341</v>
       </c>
       <c r="R19" t="n">
-        <v>7204281</v>
+        <v>7204156</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210221</v>
+        <v>113210232</v>
       </c>
       <c r="B20" t="n">
-        <v>79185</v>
+        <v>79230</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
         <v>113210275</v>
       </c>
       <c r="B21" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210195</v>
+        <v>113210206</v>
       </c>
       <c r="B22" t="n">
-        <v>56765</v>
+        <v>79223</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,43 +2942,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543458</v>
+        <v>543426</v>
       </c>
       <c r="R22" t="n">
-        <v>7204009</v>
+        <v>7204342</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210266</v>
+        <v>113210269</v>
       </c>
       <c r="B23" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543399</v>
+        <v>543356</v>
       </c>
       <c r="R23" t="n">
-        <v>7204037</v>
+        <v>7204196</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210200</v>
+        <v>113210264</v>
       </c>
       <c r="B24" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,39 +3170,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543369</v>
+        <v>543460</v>
       </c>
       <c r="R24" t="n">
-        <v>7204270</v>
+        <v>7204008</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210194</v>
+        <v>113210261</v>
       </c>
       <c r="B25" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,39 +3282,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543464</v>
+        <v>543502</v>
       </c>
       <c r="R25" t="n">
-        <v>7204006</v>
+        <v>7203971</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,10 +3378,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210193</v>
+        <v>113210195</v>
       </c>
       <c r="B26" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543467</v>
+        <v>543458</v>
       </c>
       <c r="R26" t="n">
-        <v>7203980</v>
+        <v>7204009</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3473,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210229</v>
+        <v>113210234</v>
       </c>
       <c r="B27" t="n">
-        <v>79184</v>
+        <v>77114</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,21 +3511,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3550,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543341</v>
+        <v>543438</v>
       </c>
       <c r="R27" t="n">
-        <v>7204156</v>
+        <v>7204529</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3585,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3622,10 +3607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210264</v>
+        <v>113210221</v>
       </c>
       <c r="B28" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3638,21 +3623,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3662,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543460</v>
+        <v>543400</v>
       </c>
       <c r="R28" t="n">
-        <v>7204008</v>
+        <v>7204030</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3697,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3707,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,10 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210262</v>
+        <v>113210220</v>
       </c>
       <c r="B29" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543464</v>
+        <v>543501</v>
       </c>
       <c r="R29" t="n">
-        <v>7203981</v>
+        <v>7203965</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210220</v>
+        <v>113210274</v>
       </c>
       <c r="B30" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,21 +3847,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543501</v>
+        <v>543417</v>
       </c>
       <c r="R30" t="n">
-        <v>7203965</v>
+        <v>7204383</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210261</v>
+        <v>113210193</v>
       </c>
       <c r="B31" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,34 +3959,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543502</v>
+        <v>543467</v>
       </c>
       <c r="R31" t="n">
-        <v>7203971</v>
+        <v>7203980</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4023,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4033,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210270</v>
+        <v>113210200</v>
       </c>
       <c r="B32" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,24 +4076,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
@@ -4182,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210201</v>
+        <v>113210267</v>
       </c>
       <c r="B33" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,39 +4193,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543371</v>
+        <v>543370</v>
       </c>
       <c r="R33" t="n">
-        <v>7204278</v>
+        <v>7204023</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4262,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4272,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4299,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210232</v>
+        <v>113210271</v>
       </c>
       <c r="B34" t="n">
-        <v>79218</v>
+        <v>78133</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,25 +4301,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4339,10 +4329,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543400</v>
+        <v>543369</v>
       </c>
       <c r="R34" t="n">
-        <v>7204030</v>
+        <v>7204284</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4374,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,10 +4401,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210188</v>
+        <v>113210223</v>
       </c>
       <c r="B35" t="n">
-        <v>74302</v>
+        <v>79130</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4423,25 +4413,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4451,10 +4441,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543416</v>
+        <v>543414</v>
       </c>
       <c r="R35" t="n">
-        <v>7204379</v>
+        <v>7204395</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4486,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210186</v>
+        <v>113210219</v>
       </c>
       <c r="B36" t="n">
-        <v>74302</v>
+        <v>79197</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,21 +4529,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4563,10 +4553,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543457</v>
+        <v>543507</v>
       </c>
       <c r="R36" t="n">
-        <v>7204024</v>
+        <v>7203943</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4625,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210239</v>
+        <v>113210222</v>
       </c>
       <c r="B37" t="n">
-        <v>90063</v>
+        <v>79197</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,21 +4641,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4675,10 +4665,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543380</v>
+        <v>543338</v>
       </c>
       <c r="R37" t="n">
-        <v>7204272</v>
+        <v>7204158</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4737,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210259</v>
+        <v>113210194</v>
       </c>
       <c r="B38" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4763,34 +4753,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543507</v>
+        <v>543464</v>
       </c>
       <c r="R38" t="n">
-        <v>7203943</v>
+        <v>7204006</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4827,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210263</v>
+        <v>113210196</v>
       </c>
       <c r="B39" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,34 +4870,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543461</v>
+        <v>543372</v>
       </c>
       <c r="R39" t="n">
-        <v>7204010</v>
+        <v>7204028</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210273</v>
+        <v>113210219</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543426</v>
+        <v>543507</v>
       </c>
       <c r="R2" t="n">
-        <v>7204339</v>
+        <v>7203943</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210201</v>
+        <v>113210194</v>
       </c>
       <c r="B3" t="n">
         <v>56766</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543371</v>
+        <v>543464</v>
       </c>
       <c r="R3" t="n">
-        <v>7204278</v>
+        <v>7204006</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210270</v>
+        <v>113210266</v>
       </c>
       <c r="B4" t="n">
         <v>78133</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543369</v>
+        <v>543399</v>
       </c>
       <c r="R4" t="n">
-        <v>7204270</v>
+        <v>7204037</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210272</v>
+        <v>113210261</v>
       </c>
       <c r="B5" t="n">
         <v>78133</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543381</v>
+        <v>543502</v>
       </c>
       <c r="R5" t="n">
-        <v>7204285</v>
+        <v>7203971</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210198</v>
+        <v>113210239</v>
       </c>
       <c r="B6" t="n">
-        <v>56766</v>
+        <v>90075</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543348</v>
+        <v>543380</v>
       </c>
       <c r="R6" t="n">
-        <v>7204165</v>
+        <v>7204272</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210266</v>
+        <v>113210275</v>
       </c>
       <c r="B7" t="n">
         <v>78133</v>
@@ -1285,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543399</v>
+        <v>543411</v>
       </c>
       <c r="R7" t="n">
-        <v>7204037</v>
+        <v>7204394</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210199</v>
+        <v>113210223</v>
       </c>
       <c r="B8" t="n">
-        <v>56766</v>
+        <v>79130</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,43 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543356</v>
+        <v>543414</v>
       </c>
       <c r="R8" t="n">
-        <v>7204193</v>
+        <v>7204395</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210239</v>
+        <v>113210229</v>
       </c>
       <c r="B9" t="n">
-        <v>90075</v>
+        <v>79196</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543380</v>
+        <v>543341</v>
       </c>
       <c r="R9" t="n">
-        <v>7204272</v>
+        <v>7204156</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210187</v>
+        <v>113210193</v>
       </c>
       <c r="B10" t="n">
-        <v>74314</v>
+        <v>56766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,34 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543382</v>
+        <v>543467</v>
       </c>
       <c r="R10" t="n">
-        <v>7204281</v>
+        <v>7203980</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210186</v>
+        <v>113210200</v>
       </c>
       <c r="B11" t="n">
-        <v>74314</v>
+        <v>56766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543457</v>
+        <v>543369</v>
       </c>
       <c r="R11" t="n">
-        <v>7204024</v>
+        <v>7204270</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210263</v>
+        <v>113210198</v>
       </c>
       <c r="B12" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543461</v>
+        <v>543348</v>
       </c>
       <c r="R12" t="n">
-        <v>7204010</v>
+        <v>7204165</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210265</v>
+        <v>113210220</v>
       </c>
       <c r="B13" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543457</v>
+        <v>543501</v>
       </c>
       <c r="R13" t="n">
-        <v>7204023</v>
+        <v>7203965</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2146,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210277</v>
+        <v>113210187</v>
       </c>
       <c r="B15" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543441</v>
+        <v>543382</v>
       </c>
       <c r="R15" t="n">
-        <v>7204521</v>
+        <v>7204281</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210188</v>
+        <v>113210232</v>
       </c>
       <c r="B16" t="n">
-        <v>74314</v>
+        <v>79230</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2275,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543416</v>
+        <v>543400</v>
       </c>
       <c r="R16" t="n">
-        <v>7204379</v>
+        <v>7204030</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2482,7 +2487,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210268</v>
+        <v>113210270</v>
       </c>
       <c r="B18" t="n">
         <v>78133</v>
@@ -2522,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543344</v>
+        <v>543369</v>
       </c>
       <c r="R18" t="n">
-        <v>7204178</v>
+        <v>7204270</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210229</v>
+        <v>113210277</v>
       </c>
       <c r="B19" t="n">
-        <v>79196</v>
+        <v>78133</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543341</v>
+        <v>543441</v>
       </c>
       <c r="R19" t="n">
-        <v>7204156</v>
+        <v>7204521</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210232</v>
+        <v>113210196</v>
       </c>
       <c r="B20" t="n">
-        <v>79230</v>
+        <v>56766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,38 +2723,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543400</v>
+        <v>543372</v>
       </c>
       <c r="R20" t="n">
-        <v>7204030</v>
+        <v>7204028</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,7 +2828,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210275</v>
+        <v>113210274</v>
       </c>
       <c r="B21" t="n">
         <v>78133</v>
@@ -2858,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543411</v>
+        <v>543417</v>
       </c>
       <c r="R21" t="n">
-        <v>7204394</v>
+        <v>7204383</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210206</v>
+        <v>113210268</v>
       </c>
       <c r="B22" t="n">
-        <v>79223</v>
+        <v>78133</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,25 +2952,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543426</v>
+        <v>543344</v>
       </c>
       <c r="R22" t="n">
-        <v>7204342</v>
+        <v>7204178</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,7 +3052,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210269</v>
+        <v>113210267</v>
       </c>
       <c r="B23" t="n">
         <v>78133</v>
@@ -3082,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543356</v>
+        <v>543370</v>
       </c>
       <c r="R23" t="n">
-        <v>7204196</v>
+        <v>7204023</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,7 +3164,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210264</v>
+        <v>113210263</v>
       </c>
       <c r="B24" t="n">
         <v>78133</v>
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543460</v>
+        <v>543461</v>
       </c>
       <c r="R24" t="n">
-        <v>7204008</v>
+        <v>7204010</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3229,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,7 +3276,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210261</v>
+        <v>113210269</v>
       </c>
       <c r="B25" t="n">
         <v>78133</v>
@@ -3306,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543502</v>
+        <v>543356</v>
       </c>
       <c r="R25" t="n">
-        <v>7203971</v>
+        <v>7204196</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3341,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210195</v>
+        <v>113210265</v>
       </c>
       <c r="B26" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,39 +3404,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543458</v>
+        <v>543457</v>
       </c>
       <c r="R26" t="n">
-        <v>7204009</v>
+        <v>7204023</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3458,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210234</v>
+        <v>113210264</v>
       </c>
       <c r="B27" t="n">
-        <v>77114</v>
+        <v>78133</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,21 +3516,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3535,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543438</v>
+        <v>543460</v>
       </c>
       <c r="R27" t="n">
-        <v>7204529</v>
+        <v>7204008</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3570,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,10 +3612,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210221</v>
+        <v>113210234</v>
       </c>
       <c r="B28" t="n">
-        <v>79197</v>
+        <v>77114</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,21 +3628,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3647,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543400</v>
+        <v>543438</v>
       </c>
       <c r="R28" t="n">
-        <v>7204030</v>
+        <v>7204529</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3682,7 +3687,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3697,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3724,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210220</v>
+        <v>113210195</v>
       </c>
       <c r="B29" t="n">
-        <v>79197</v>
+        <v>56766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3735,34 +3740,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543501</v>
+        <v>543458</v>
       </c>
       <c r="R29" t="n">
-        <v>7203965</v>
+        <v>7204009</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3794,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3841,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210274</v>
+        <v>113210271</v>
       </c>
       <c r="B30" t="n">
         <v>78133</v>
@@ -3871,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543417</v>
+        <v>543369</v>
       </c>
       <c r="R30" t="n">
-        <v>7204383</v>
+        <v>7204284</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210193</v>
+        <v>113210273</v>
       </c>
       <c r="B31" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,39 +3969,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543467</v>
+        <v>543426</v>
       </c>
       <c r="R31" t="n">
-        <v>7203980</v>
+        <v>7204339</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4023,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4033,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4060,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210200</v>
+        <v>113210206</v>
       </c>
       <c r="B32" t="n">
-        <v>56766</v>
+        <v>79223</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4072,43 +4077,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543369</v>
+        <v>543426</v>
       </c>
       <c r="R32" t="n">
-        <v>7204270</v>
+        <v>7204342</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210267</v>
+        <v>113210199</v>
       </c>
       <c r="B33" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,34 +4193,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543370</v>
+        <v>543356</v>
       </c>
       <c r="R33" t="n">
-        <v>7204023</v>
+        <v>7204193</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210271</v>
+        <v>113210201</v>
       </c>
       <c r="B34" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4305,34 +4310,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543369</v>
+        <v>543371</v>
       </c>
       <c r="R34" t="n">
-        <v>7204284</v>
+        <v>7204278</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4401,10 +4411,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210223</v>
+        <v>113210272</v>
       </c>
       <c r="B35" t="n">
-        <v>79130</v>
+        <v>78133</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4413,25 +4423,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4441,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543414</v>
+        <v>543381</v>
       </c>
       <c r="R35" t="n">
-        <v>7204395</v>
+        <v>7204285</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4476,7 +4486,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4486,7 +4496,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210219</v>
+        <v>113210188</v>
       </c>
       <c r="B36" t="n">
-        <v>79197</v>
+        <v>74314</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4529,21 +4539,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4553,10 +4563,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543507</v>
+        <v>543416</v>
       </c>
       <c r="R36" t="n">
-        <v>7203943</v>
+        <v>7204379</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4588,7 +4598,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4598,7 +4608,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4625,7 +4635,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210222</v>
+        <v>113210221</v>
       </c>
       <c r="B37" t="n">
         <v>79197</v>
@@ -4665,10 +4675,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543338</v>
+        <v>543400</v>
       </c>
       <c r="R37" t="n">
-        <v>7204158</v>
+        <v>7204030</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4700,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4737,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210194</v>
+        <v>113210222</v>
       </c>
       <c r="B38" t="n">
-        <v>56766</v>
+        <v>79197</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4753,39 +4763,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543464</v>
+        <v>543338</v>
       </c>
       <c r="R38" t="n">
-        <v>7204006</v>
+        <v>7204158</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4817,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210196</v>
+        <v>113210186</v>
       </c>
       <c r="B39" t="n">
-        <v>56766</v>
+        <v>74314</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4870,39 +4875,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543372</v>
+        <v>543457</v>
       </c>
       <c r="R39" t="n">
-        <v>7204028</v>
+        <v>7204024</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -3276,7 +3276,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210269</v>
+        <v>113210265</v>
       </c>
       <c r="B25" t="n">
         <v>78133</v>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543356</v>
+        <v>543457</v>
       </c>
       <c r="R25" t="n">
-        <v>7204196</v>
+        <v>7204023</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,7 +3388,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210265</v>
+        <v>113210264</v>
       </c>
       <c r="B26" t="n">
         <v>78133</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543457</v>
+        <v>543460</v>
       </c>
       <c r="R26" t="n">
-        <v>7204023</v>
+        <v>7204008</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,7 +3500,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210264</v>
+        <v>113210269</v>
       </c>
       <c r="B27" t="n">
         <v>78133</v>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543460</v>
+        <v>543356</v>
       </c>
       <c r="R27" t="n">
-        <v>7204008</v>
+        <v>7204196</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210219</v>
+        <v>113210201</v>
       </c>
       <c r="B2" t="n">
-        <v>79197</v>
+        <v>56766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543507</v>
+        <v>543371</v>
       </c>
       <c r="R2" t="n">
-        <v>7203943</v>
+        <v>7204278</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210194</v>
+        <v>113210272</v>
       </c>
       <c r="B3" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543464</v>
+        <v>543381</v>
       </c>
       <c r="R3" t="n">
-        <v>7204006</v>
+        <v>7204285</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>113210266</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210261</v>
+        <v>113210262</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543502</v>
+        <v>543464</v>
       </c>
       <c r="R5" t="n">
-        <v>7203971</v>
+        <v>7203981</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210239</v>
+        <v>113210200</v>
       </c>
       <c r="B6" t="n">
-        <v>90075</v>
+        <v>56766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543380</v>
+        <v>543369</v>
       </c>
       <c r="R6" t="n">
-        <v>7204272</v>
+        <v>7204270</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210275</v>
+        <v>113210188</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>74336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543411</v>
+        <v>543416</v>
       </c>
       <c r="R7" t="n">
-        <v>7204394</v>
+        <v>7204379</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210223</v>
+        <v>113210194</v>
       </c>
       <c r="B8" t="n">
-        <v>79130</v>
+        <v>56766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,38 +1369,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543414</v>
+        <v>543464</v>
       </c>
       <c r="R8" t="n">
-        <v>7204395</v>
+        <v>7204006</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210229</v>
+        <v>113210271</v>
       </c>
       <c r="B9" t="n">
-        <v>79196</v>
+        <v>78155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543341</v>
+        <v>543369</v>
       </c>
       <c r="R9" t="n">
-        <v>7204156</v>
+        <v>7204284</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210193</v>
+        <v>113210268</v>
       </c>
       <c r="B10" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543467</v>
+        <v>543344</v>
       </c>
       <c r="R10" t="n">
-        <v>7203980</v>
+        <v>7204178</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210200</v>
+        <v>113210239</v>
       </c>
       <c r="B11" t="n">
-        <v>56766</v>
+        <v>90097</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543369</v>
+        <v>543380</v>
       </c>
       <c r="R11" t="n">
-        <v>7204270</v>
+        <v>7204272</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210198</v>
+        <v>113210259</v>
       </c>
       <c r="B12" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1826,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543348</v>
+        <v>543507</v>
       </c>
       <c r="R12" t="n">
-        <v>7204165</v>
+        <v>7203943</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210220</v>
+        <v>113210221</v>
       </c>
       <c r="B13" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543501</v>
+        <v>543400</v>
       </c>
       <c r="R13" t="n">
-        <v>7203965</v>
+        <v>7204030</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210262</v>
+        <v>113210270</v>
       </c>
       <c r="B14" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543464</v>
+        <v>543369</v>
       </c>
       <c r="R14" t="n">
-        <v>7203981</v>
+        <v>7204270</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210187</v>
+        <v>113210261</v>
       </c>
       <c r="B15" t="n">
-        <v>74314</v>
+        <v>78155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543382</v>
+        <v>543502</v>
       </c>
       <c r="R15" t="n">
-        <v>7204281</v>
+        <v>7203971</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210232</v>
+        <v>113210186</v>
       </c>
       <c r="B16" t="n">
-        <v>79230</v>
+        <v>74336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,25 +2270,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543400</v>
+        <v>543457</v>
       </c>
       <c r="R16" t="n">
-        <v>7204030</v>
+        <v>7204024</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210259</v>
+        <v>113210195</v>
       </c>
       <c r="B17" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,34 +2386,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543507</v>
+        <v>543458</v>
       </c>
       <c r="R17" t="n">
-        <v>7203943</v>
+        <v>7204009</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210270</v>
+        <v>113210274</v>
       </c>
       <c r="B18" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543369</v>
+        <v>543417</v>
       </c>
       <c r="R18" t="n">
-        <v>7204270</v>
+        <v>7204383</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210277</v>
+        <v>113210199</v>
       </c>
       <c r="B19" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,34 +2615,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543441</v>
+        <v>543356</v>
       </c>
       <c r="R19" t="n">
-        <v>7204521</v>
+        <v>7204193</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210196</v>
+        <v>113210219</v>
       </c>
       <c r="B20" t="n">
-        <v>56766</v>
+        <v>79219</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,39 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543372</v>
+        <v>543507</v>
       </c>
       <c r="R20" t="n">
-        <v>7204028</v>
+        <v>7203943</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210274</v>
+        <v>113210223</v>
       </c>
       <c r="B21" t="n">
-        <v>78133</v>
+        <v>79152</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2840,25 +2840,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543417</v>
+        <v>543414</v>
       </c>
       <c r="R21" t="n">
-        <v>7204383</v>
+        <v>7204395</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210268</v>
+        <v>113210234</v>
       </c>
       <c r="B22" t="n">
-        <v>78133</v>
+        <v>77136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543344</v>
+        <v>543438</v>
       </c>
       <c r="R22" t="n">
-        <v>7204178</v>
+        <v>7204529</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210267</v>
+        <v>113210198</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,34 +3068,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543370</v>
+        <v>543348</v>
       </c>
       <c r="R23" t="n">
-        <v>7204023</v>
+        <v>7204165</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210263</v>
+        <v>113210264</v>
       </c>
       <c r="B24" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,10 +3209,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543461</v>
+        <v>543460</v>
       </c>
       <c r="R24" t="n">
-        <v>7204010</v>
+        <v>7204008</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210265</v>
+        <v>113210263</v>
       </c>
       <c r="B25" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,10 +3321,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543457</v>
+        <v>543461</v>
       </c>
       <c r="R25" t="n">
-        <v>7204023</v>
+        <v>7204010</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3351,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210264</v>
+        <v>113210196</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3404,34 +3409,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543460</v>
+        <v>543372</v>
       </c>
       <c r="R26" t="n">
-        <v>7204008</v>
+        <v>7204028</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210269</v>
+        <v>113210222</v>
       </c>
       <c r="B27" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3516,21 +3526,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3550,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543356</v>
+        <v>543338</v>
       </c>
       <c r="R27" t="n">
-        <v>7204196</v>
+        <v>7204158</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3575,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210234</v>
+        <v>113210277</v>
       </c>
       <c r="B28" t="n">
-        <v>77114</v>
+        <v>78155</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,21 +3638,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3652,10 +3662,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543438</v>
+        <v>543441</v>
       </c>
       <c r="R28" t="n">
-        <v>7204529</v>
+        <v>7204521</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3724,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210195</v>
+        <v>113210269</v>
       </c>
       <c r="B29" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3740,39 +3750,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543458</v>
+        <v>543356</v>
       </c>
       <c r="R29" t="n">
-        <v>7204009</v>
+        <v>7204196</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210271</v>
+        <v>113210206</v>
       </c>
       <c r="B30" t="n">
-        <v>78133</v>
+        <v>79245</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,25 +3858,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543369</v>
+        <v>543426</v>
       </c>
       <c r="R30" t="n">
-        <v>7204284</v>
+        <v>7204342</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3916,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210273</v>
+        <v>113210232</v>
       </c>
       <c r="B31" t="n">
-        <v>78133</v>
+        <v>79252</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3965,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543426</v>
+        <v>543400</v>
       </c>
       <c r="R31" t="n">
-        <v>7204339</v>
+        <v>7204030</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210206</v>
+        <v>113210220</v>
       </c>
       <c r="B32" t="n">
-        <v>79223</v>
+        <v>79219</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4077,25 +4082,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543426</v>
+        <v>543501</v>
       </c>
       <c r="R32" t="n">
-        <v>7204342</v>
+        <v>7203965</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4140,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210199</v>
+        <v>113210273</v>
       </c>
       <c r="B33" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,39 +4198,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543356</v>
+        <v>543426</v>
       </c>
       <c r="R33" t="n">
-        <v>7204193</v>
+        <v>7204339</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210201</v>
+        <v>113210187</v>
       </c>
       <c r="B34" t="n">
-        <v>56766</v>
+        <v>74336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,39 +4310,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543371</v>
+        <v>543382</v>
       </c>
       <c r="R34" t="n">
-        <v>7204278</v>
+        <v>7204281</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4374,7 +4369,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4384,7 +4379,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4411,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210272</v>
+        <v>113210275</v>
       </c>
       <c r="B35" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,10 +4446,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543381</v>
+        <v>543411</v>
       </c>
       <c r="R35" t="n">
-        <v>7204285</v>
+        <v>7204394</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4486,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4496,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210188</v>
+        <v>113210193</v>
       </c>
       <c r="B36" t="n">
-        <v>74314</v>
+        <v>56766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4539,34 +4534,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543416</v>
+        <v>543467</v>
       </c>
       <c r="R36" t="n">
-        <v>7204379</v>
+        <v>7203980</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4635,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210221</v>
+        <v>113210265</v>
       </c>
       <c r="B37" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,21 +4651,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4675,10 +4675,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543400</v>
+        <v>543457</v>
       </c>
       <c r="R37" t="n">
-        <v>7204030</v>
+        <v>7204023</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210222</v>
+        <v>113210229</v>
       </c>
       <c r="B38" t="n">
-        <v>79197</v>
+        <v>79218</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543338</v>
+        <v>543341</v>
       </c>
       <c r="R38" t="n">
-        <v>7204158</v>
+        <v>7204156</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210186</v>
+        <v>113210267</v>
       </c>
       <c r="B39" t="n">
-        <v>74314</v>
+        <v>78155</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543457</v>
+        <v>543370</v>
       </c>
       <c r="R39" t="n">
-        <v>7204024</v>
+        <v>7204023</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -3734,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210269</v>
+        <v>113210232</v>
       </c>
       <c r="B29" t="n">
-        <v>78155</v>
+        <v>79252</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3746,25 +3746,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543356</v>
+        <v>543400</v>
       </c>
       <c r="R29" t="n">
-        <v>7204196</v>
+        <v>7204030</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210206</v>
+        <v>113210220</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79219</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543426</v>
+        <v>543501</v>
       </c>
       <c r="R30" t="n">
-        <v>7204342</v>
+        <v>7203965</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210232</v>
+        <v>113210269</v>
       </c>
       <c r="B31" t="n">
-        <v>79252</v>
+        <v>78155</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543400</v>
+        <v>543356</v>
       </c>
       <c r="R31" t="n">
-        <v>7204030</v>
+        <v>7204196</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210220</v>
+        <v>113210206</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79245</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,25 +4082,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543501</v>
+        <v>543426</v>
       </c>
       <c r="R32" t="n">
-        <v>7203965</v>
+        <v>7204342</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210201</v>
+        <v>113210261</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543371</v>
+        <v>543502</v>
       </c>
       <c r="R2" t="n">
-        <v>7204278</v>
+        <v>7203971</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210272</v>
+        <v>113210267</v>
       </c>
       <c r="B3" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543381</v>
+        <v>543370</v>
       </c>
       <c r="R3" t="n">
-        <v>7204285</v>
+        <v>7204023</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210266</v>
+        <v>113210222</v>
       </c>
       <c r="B4" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543399</v>
+        <v>543338</v>
       </c>
       <c r="R4" t="n">
-        <v>7204037</v>
+        <v>7204158</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210262</v>
+        <v>113210206</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>79249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543464</v>
+        <v>543426</v>
       </c>
       <c r="R5" t="n">
-        <v>7203981</v>
+        <v>7204342</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210200</v>
+        <v>113210195</v>
       </c>
       <c r="B6" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543369</v>
+        <v>543458</v>
       </c>
       <c r="R6" t="n">
-        <v>7204270</v>
+        <v>7204009</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210188</v>
+        <v>113210201</v>
       </c>
       <c r="B7" t="n">
-        <v>74336</v>
+        <v>56769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543416</v>
+        <v>543371</v>
       </c>
       <c r="R7" t="n">
-        <v>7204379</v>
+        <v>7204278</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210194</v>
+        <v>113210262</v>
       </c>
       <c r="B8" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,29 +1373,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
@@ -1405,7 +1400,7 @@
         <v>543464</v>
       </c>
       <c r="R8" t="n">
-        <v>7204006</v>
+        <v>7203981</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210271</v>
+        <v>113210263</v>
       </c>
       <c r="B9" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543369</v>
+        <v>543461</v>
       </c>
       <c r="R9" t="n">
-        <v>7204284</v>
+        <v>7204010</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210268</v>
+        <v>113210188</v>
       </c>
       <c r="B10" t="n">
-        <v>78155</v>
+        <v>74339</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543344</v>
+        <v>543416</v>
       </c>
       <c r="R10" t="n">
-        <v>7204178</v>
+        <v>7204379</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210239</v>
+        <v>113210220</v>
       </c>
       <c r="B11" t="n">
-        <v>90097</v>
+        <v>79223</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1709,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543380</v>
+        <v>543501</v>
       </c>
       <c r="R11" t="n">
-        <v>7204272</v>
+        <v>7203965</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210259</v>
+        <v>113210269</v>
       </c>
       <c r="B12" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543507</v>
+        <v>543356</v>
       </c>
       <c r="R12" t="n">
-        <v>7203943</v>
+        <v>7204196</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210221</v>
+        <v>113210266</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543400</v>
+        <v>543399</v>
       </c>
       <c r="R13" t="n">
-        <v>7204030</v>
+        <v>7204037</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2032,7 @@
         <v>113210270</v>
       </c>
       <c r="B14" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210261</v>
+        <v>113210274</v>
       </c>
       <c r="B15" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543502</v>
+        <v>543417</v>
       </c>
       <c r="R15" t="n">
-        <v>7203971</v>
+        <v>7204383</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210186</v>
+        <v>113210277</v>
       </c>
       <c r="B16" t="n">
-        <v>74336</v>
+        <v>78158</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543457</v>
+        <v>543441</v>
       </c>
       <c r="R16" t="n">
-        <v>7204024</v>
+        <v>7204521</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210195</v>
+        <v>113210193</v>
       </c>
       <c r="B17" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543458</v>
+        <v>543467</v>
       </c>
       <c r="R17" t="n">
-        <v>7204009</v>
+        <v>7203980</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210274</v>
+        <v>113210265</v>
       </c>
       <c r="B18" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543417</v>
+        <v>543457</v>
       </c>
       <c r="R18" t="n">
-        <v>7204383</v>
+        <v>7204023</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210199</v>
+        <v>113210229</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>79222</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,39 +2610,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543356</v>
+        <v>543341</v>
       </c>
       <c r="R19" t="n">
-        <v>7204193</v>
+        <v>7204156</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210219</v>
+        <v>113210232</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79256</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543507</v>
+        <v>543400</v>
       </c>
       <c r="R20" t="n">
-        <v>7203943</v>
+        <v>7204030</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210223</v>
+        <v>113210196</v>
       </c>
       <c r="B21" t="n">
-        <v>79152</v>
+        <v>56769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2840,38 +2830,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543414</v>
+        <v>543372</v>
       </c>
       <c r="R21" t="n">
-        <v>7204395</v>
+        <v>7204028</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2908,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210234</v>
+        <v>113210275</v>
       </c>
       <c r="B22" t="n">
-        <v>77136</v>
+        <v>78158</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543438</v>
+        <v>543411</v>
       </c>
       <c r="R22" t="n">
-        <v>7204529</v>
+        <v>7204394</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210198</v>
+        <v>113210194</v>
       </c>
       <c r="B23" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3097,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543348</v>
+        <v>543464</v>
       </c>
       <c r="R23" t="n">
-        <v>7204165</v>
+        <v>7204006</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3132,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210264</v>
+        <v>113210198</v>
       </c>
       <c r="B24" t="n">
-        <v>78155</v>
+        <v>56769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3185,34 +3180,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543460</v>
+        <v>543348</v>
       </c>
       <c r="R24" t="n">
-        <v>7204008</v>
+        <v>7204165</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210263</v>
+        <v>113210234</v>
       </c>
       <c r="B25" t="n">
-        <v>78155</v>
+        <v>77139</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543461</v>
+        <v>543438</v>
       </c>
       <c r="R25" t="n">
-        <v>7204010</v>
+        <v>7204529</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210196</v>
+        <v>113210186</v>
       </c>
       <c r="B26" t="n">
-        <v>56766</v>
+        <v>74339</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3409,39 +3409,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543372</v>
+        <v>543457</v>
       </c>
       <c r="R26" t="n">
-        <v>7204028</v>
+        <v>7204024</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3473,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3505,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210222</v>
+        <v>113210239</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>90101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,21 +3521,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543338</v>
+        <v>543380</v>
       </c>
       <c r="R27" t="n">
-        <v>7204158</v>
+        <v>7204272</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3585,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3622,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210277</v>
+        <v>113210187</v>
       </c>
       <c r="B28" t="n">
-        <v>78155</v>
+        <v>74339</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3638,21 +3633,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3662,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543441</v>
+        <v>543382</v>
       </c>
       <c r="R28" t="n">
-        <v>7204521</v>
+        <v>7204281</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3697,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3707,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,10 +3729,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210232</v>
+        <v>113210259</v>
       </c>
       <c r="B29" t="n">
-        <v>79252</v>
+        <v>78158</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3746,25 +3741,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3774,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543400</v>
+        <v>543507</v>
       </c>
       <c r="R29" t="n">
-        <v>7204030</v>
+        <v>7203943</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3809,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3819,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210220</v>
+        <v>113210268</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,21 +3857,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543501</v>
+        <v>543344</v>
       </c>
       <c r="R30" t="n">
-        <v>7203965</v>
+        <v>7204178</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3921,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3931,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210269</v>
+        <v>113210221</v>
       </c>
       <c r="B31" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3969,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543356</v>
+        <v>543400</v>
       </c>
       <c r="R31" t="n">
-        <v>7204196</v>
+        <v>7204030</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4033,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210206</v>
+        <v>113210199</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>56769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,38 +4077,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543426</v>
+        <v>543356</v>
       </c>
       <c r="R32" t="n">
-        <v>7204342</v>
+        <v>7204193</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210273</v>
+        <v>113210272</v>
       </c>
       <c r="B33" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543426</v>
+        <v>543381</v>
       </c>
       <c r="R33" t="n">
-        <v>7204339</v>
+        <v>7204285</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210187</v>
+        <v>113210219</v>
       </c>
       <c r="B34" t="n">
-        <v>74336</v>
+        <v>79223</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,21 +4310,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543382</v>
+        <v>543507</v>
       </c>
       <c r="R34" t="n">
-        <v>7204281</v>
+        <v>7203943</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210275</v>
+        <v>113210264</v>
       </c>
       <c r="B35" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543411</v>
+        <v>543460</v>
       </c>
       <c r="R35" t="n">
-        <v>7204394</v>
+        <v>7204008</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210193</v>
+        <v>113210271</v>
       </c>
       <c r="B36" t="n">
-        <v>56766</v>
+        <v>78158</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,39 +4534,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543467</v>
+        <v>543369</v>
       </c>
       <c r="R36" t="n">
-        <v>7203980</v>
+        <v>7204284</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4598,7 +4593,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4608,7 +4603,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4635,10 +4630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210265</v>
+        <v>113210273</v>
       </c>
       <c r="B37" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4675,10 +4670,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543457</v>
+        <v>543426</v>
       </c>
       <c r="R37" t="n">
-        <v>7204023</v>
+        <v>7204339</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4705,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4715,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4742,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210229</v>
+        <v>113210200</v>
       </c>
       <c r="B38" t="n">
-        <v>79218</v>
+        <v>56769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4763,34 +4758,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543341</v>
+        <v>543369</v>
       </c>
       <c r="R38" t="n">
-        <v>7204156</v>
+        <v>7204270</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210267</v>
+        <v>113210223</v>
       </c>
       <c r="B39" t="n">
-        <v>78155</v>
+        <v>79156</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4871,25 +4871,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543370</v>
+        <v>543414</v>
       </c>
       <c r="R39" t="n">
-        <v>7204023</v>
+        <v>7204395</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -2029,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210270</v>
+        <v>113210193</v>
       </c>
       <c r="B14" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,34 +2045,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543369</v>
+        <v>543467</v>
       </c>
       <c r="R14" t="n">
-        <v>7204270</v>
+        <v>7203980</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210274</v>
+        <v>113210270</v>
       </c>
       <c r="B15" t="n">
         <v>78158</v>
@@ -2181,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543417</v>
+        <v>543369</v>
       </c>
       <c r="R15" t="n">
-        <v>7204383</v>
+        <v>7204270</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,7 +2258,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210277</v>
+        <v>113210274</v>
       </c>
       <c r="B16" t="n">
         <v>78158</v>
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543441</v>
+        <v>543417</v>
       </c>
       <c r="R16" t="n">
-        <v>7204521</v>
+        <v>7204383</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210193</v>
+        <v>113210277</v>
       </c>
       <c r="B17" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,39 +2386,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543467</v>
+        <v>543441</v>
       </c>
       <c r="R17" t="n">
-        <v>7203980</v>
+        <v>7204521</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2935,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210275</v>
+        <v>113210194</v>
       </c>
       <c r="B22" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,34 +2951,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543411</v>
+        <v>543464</v>
       </c>
       <c r="R22" t="n">
-        <v>7204394</v>
+        <v>7204006</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,7 +3052,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210194</v>
+        <v>113210198</v>
       </c>
       <c r="B23" t="n">
         <v>56769</v>
@@ -3092,10 +3097,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543464</v>
+        <v>543348</v>
       </c>
       <c r="R23" t="n">
-        <v>7204006</v>
+        <v>7204165</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210198</v>
+        <v>113210234</v>
       </c>
       <c r="B24" t="n">
-        <v>56769</v>
+        <v>77139</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,39 +3185,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543348</v>
+        <v>543438</v>
       </c>
       <c r="R24" t="n">
-        <v>7204165</v>
+        <v>7204529</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210234</v>
+        <v>113210275</v>
       </c>
       <c r="B25" t="n">
-        <v>77139</v>
+        <v>78158</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3297,21 +3297,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3321,10 +3321,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543438</v>
+        <v>543411</v>
       </c>
       <c r="R25" t="n">
-        <v>7204529</v>
+        <v>7204394</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210261</v>
+        <v>113210271</v>
       </c>
       <c r="B2" t="n">
         <v>78158</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543502</v>
+        <v>543369</v>
       </c>
       <c r="R2" t="n">
-        <v>7203971</v>
+        <v>7204284</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210267</v>
+        <v>113210219</v>
       </c>
       <c r="B3" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543370</v>
+        <v>543507</v>
       </c>
       <c r="R3" t="n">
-        <v>7204023</v>
+        <v>7203943</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210222</v>
+        <v>113210206</v>
       </c>
       <c r="B4" t="n">
-        <v>79223</v>
+        <v>79249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543338</v>
+        <v>543426</v>
       </c>
       <c r="R4" t="n">
-        <v>7204158</v>
+        <v>7204342</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210206</v>
+        <v>113210198</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>56769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543426</v>
+        <v>543348</v>
       </c>
       <c r="R5" t="n">
-        <v>7204342</v>
+        <v>7204165</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210195</v>
+        <v>113210222</v>
       </c>
       <c r="B6" t="n">
-        <v>56769</v>
+        <v>79223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543458</v>
+        <v>543338</v>
       </c>
       <c r="R6" t="n">
-        <v>7204009</v>
+        <v>7204158</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210201</v>
+        <v>113210268</v>
       </c>
       <c r="B7" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543371</v>
+        <v>543344</v>
       </c>
       <c r="R7" t="n">
-        <v>7204278</v>
+        <v>7204178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210262</v>
+        <v>113210220</v>
       </c>
       <c r="B8" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543464</v>
+        <v>543501</v>
       </c>
       <c r="R8" t="n">
-        <v>7203981</v>
+        <v>7203965</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210188</v>
+        <v>113210200</v>
       </c>
       <c r="B10" t="n">
-        <v>74339</v>
+        <v>56769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543416</v>
+        <v>543369</v>
       </c>
       <c r="R10" t="n">
-        <v>7204379</v>
+        <v>7204270</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210220</v>
+        <v>113210201</v>
       </c>
       <c r="B11" t="n">
-        <v>79223</v>
+        <v>56769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543501</v>
+        <v>543371</v>
       </c>
       <c r="R11" t="n">
-        <v>7203965</v>
+        <v>7204278</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210269</v>
+        <v>113210223</v>
       </c>
       <c r="B12" t="n">
-        <v>78158</v>
+        <v>79156</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,25 +1822,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543356</v>
+        <v>543414</v>
       </c>
       <c r="R12" t="n">
-        <v>7204196</v>
+        <v>7204395</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1922,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210266</v>
+        <v>113210262</v>
       </c>
       <c r="B13" t="n">
         <v>78158</v>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543399</v>
+        <v>543464</v>
       </c>
       <c r="R13" t="n">
-        <v>7204037</v>
+        <v>7203981</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210193</v>
+        <v>113210261</v>
       </c>
       <c r="B14" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,39 +2050,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543467</v>
+        <v>543502</v>
       </c>
       <c r="R14" t="n">
-        <v>7203980</v>
+        <v>7203971</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,7 +2258,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210274</v>
+        <v>113210275</v>
       </c>
       <c r="B16" t="n">
         <v>78158</v>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543417</v>
+        <v>543411</v>
       </c>
       <c r="R16" t="n">
-        <v>7204383</v>
+        <v>7204394</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2370,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210277</v>
+        <v>113210269</v>
       </c>
       <c r="B17" t="n">
         <v>78158</v>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543441</v>
+        <v>543356</v>
       </c>
       <c r="R17" t="n">
-        <v>7204521</v>
+        <v>7204196</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210229</v>
+        <v>113210186</v>
       </c>
       <c r="B19" t="n">
-        <v>79222</v>
+        <v>74339</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543341</v>
+        <v>543457</v>
       </c>
       <c r="R19" t="n">
-        <v>7204156</v>
+        <v>7204024</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210232</v>
+        <v>113210274</v>
       </c>
       <c r="B20" t="n">
-        <v>79256</v>
+        <v>78158</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543400</v>
+        <v>543417</v>
       </c>
       <c r="R20" t="n">
-        <v>7204030</v>
+        <v>7204383</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210196</v>
+        <v>113210267</v>
       </c>
       <c r="B21" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,39 +2834,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543372</v>
+        <v>543370</v>
       </c>
       <c r="R21" t="n">
-        <v>7204028</v>
+        <v>7204023</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2935,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210194</v>
+        <v>113210195</v>
       </c>
       <c r="B22" t="n">
         <v>56769</v>
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543464</v>
+        <v>543458</v>
       </c>
       <c r="R22" t="n">
-        <v>7204006</v>
+        <v>7204009</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210198</v>
+        <v>113210187</v>
       </c>
       <c r="B23" t="n">
-        <v>56769</v>
+        <v>74339</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,39 +3063,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543348</v>
+        <v>543382</v>
       </c>
       <c r="R23" t="n">
-        <v>7204165</v>
+        <v>7204281</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3132,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210234</v>
+        <v>113210277</v>
       </c>
       <c r="B24" t="n">
-        <v>77139</v>
+        <v>78158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3185,21 +3175,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3209,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543438</v>
+        <v>543441</v>
       </c>
       <c r="R24" t="n">
-        <v>7204529</v>
+        <v>7204521</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3281,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210275</v>
+        <v>113210221</v>
       </c>
       <c r="B25" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3297,21 +3287,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3321,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543411</v>
+        <v>543400</v>
       </c>
       <c r="R25" t="n">
-        <v>7204394</v>
+        <v>7204030</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3393,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210186</v>
+        <v>113210229</v>
       </c>
       <c r="B26" t="n">
-        <v>74339</v>
+        <v>79222</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3409,21 +3399,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3433,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543457</v>
+        <v>543341</v>
       </c>
       <c r="R26" t="n">
-        <v>7204024</v>
+        <v>7204156</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3468,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3617,10 +3607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210187</v>
+        <v>113210232</v>
       </c>
       <c r="B28" t="n">
-        <v>74339</v>
+        <v>79256</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3629,25 +3619,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3657,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543382</v>
+        <v>543400</v>
       </c>
       <c r="R28" t="n">
-        <v>7204281</v>
+        <v>7204030</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3692,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,7 +3719,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210259</v>
+        <v>113210266</v>
       </c>
       <c r="B29" t="n">
         <v>78158</v>
@@ -3769,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543507</v>
+        <v>543399</v>
       </c>
       <c r="R29" t="n">
-        <v>7203943</v>
+        <v>7204037</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210268</v>
+        <v>113210193</v>
       </c>
       <c r="B30" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,34 +3847,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543344</v>
+        <v>543467</v>
       </c>
       <c r="R30" t="n">
-        <v>7204178</v>
+        <v>7203980</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3916,7 +3911,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3921,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210221</v>
+        <v>113210194</v>
       </c>
       <c r="B31" t="n">
-        <v>79223</v>
+        <v>56769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,34 +3964,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543400</v>
+        <v>543464</v>
       </c>
       <c r="R31" t="n">
-        <v>7204030</v>
+        <v>7204006</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210199</v>
+        <v>113210264</v>
       </c>
       <c r="B32" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4081,39 +4081,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543356</v>
+        <v>543460</v>
       </c>
       <c r="R32" t="n">
-        <v>7204193</v>
+        <v>7204008</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4145,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,7 +4177,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210272</v>
+        <v>113210259</v>
       </c>
       <c r="B33" t="n">
         <v>78158</v>
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543381</v>
+        <v>543507</v>
       </c>
       <c r="R33" t="n">
-        <v>7204285</v>
+        <v>7203943</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4257,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4294,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210219</v>
+        <v>113210272</v>
       </c>
       <c r="B34" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,21 +4305,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,10 +4329,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543507</v>
+        <v>543381</v>
       </c>
       <c r="R34" t="n">
-        <v>7203943</v>
+        <v>7204285</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,7 +4401,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210264</v>
+        <v>113210273</v>
       </c>
       <c r="B35" t="n">
         <v>78158</v>
@@ -4446,10 +4441,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543460</v>
+        <v>543426</v>
       </c>
       <c r="R35" t="n">
-        <v>7204008</v>
+        <v>7204339</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210271</v>
+        <v>113210199</v>
       </c>
       <c r="B36" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,34 +4529,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543369</v>
+        <v>543356</v>
       </c>
       <c r="R36" t="n">
-        <v>7204284</v>
+        <v>7204193</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,10 +4630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210273</v>
+        <v>113210196</v>
       </c>
       <c r="B37" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,34 +4646,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543426</v>
+        <v>543372</v>
       </c>
       <c r="R37" t="n">
-        <v>7204339</v>
+        <v>7204028</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4705,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4715,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4742,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210200</v>
+        <v>113210188</v>
       </c>
       <c r="B38" t="n">
-        <v>56769</v>
+        <v>74339</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4758,39 +4763,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543369</v>
+        <v>543416</v>
       </c>
       <c r="R38" t="n">
-        <v>7204270</v>
+        <v>7204379</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210223</v>
+        <v>113210234</v>
       </c>
       <c r="B39" t="n">
-        <v>79156</v>
+        <v>77139</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4871,25 +4871,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543414</v>
+        <v>543438</v>
       </c>
       <c r="R39" t="n">
-        <v>7204395</v>
+        <v>7204529</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210271</v>
+        <v>113210187</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>74345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543369</v>
+        <v>543382</v>
       </c>
       <c r="R2" t="n">
-        <v>7204284</v>
+        <v>7204281</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210219</v>
+        <v>113210275</v>
       </c>
       <c r="B3" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543507</v>
+        <v>543411</v>
       </c>
       <c r="R3" t="n">
-        <v>7203943</v>
+        <v>7204394</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210206</v>
+        <v>113210201</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>56773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543426</v>
+        <v>543371</v>
       </c>
       <c r="R4" t="n">
-        <v>7204342</v>
+        <v>7204278</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210198</v>
+        <v>113210271</v>
       </c>
       <c r="B5" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543348</v>
+        <v>543369</v>
       </c>
       <c r="R5" t="n">
-        <v>7204165</v>
+        <v>7204284</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210222</v>
+        <v>113210267</v>
       </c>
       <c r="B6" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543338</v>
+        <v>543370</v>
       </c>
       <c r="R6" t="n">
-        <v>7204158</v>
+        <v>7204023</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210268</v>
+        <v>113210266</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543344</v>
+        <v>543399</v>
       </c>
       <c r="R7" t="n">
-        <v>7204178</v>
+        <v>7204037</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210220</v>
+        <v>113210262</v>
       </c>
       <c r="B8" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543501</v>
+        <v>543464</v>
       </c>
       <c r="R8" t="n">
-        <v>7203965</v>
+        <v>7203981</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210263</v>
+        <v>113210200</v>
       </c>
       <c r="B9" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543461</v>
+        <v>543369</v>
       </c>
       <c r="R9" t="n">
-        <v>7204010</v>
+        <v>7204270</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210200</v>
+        <v>113210270</v>
       </c>
       <c r="B10" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,29 +1597,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113210201</v>
+        <v>113210239</v>
       </c>
       <c r="B11" t="n">
-        <v>56769</v>
+        <v>90107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1709,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543371</v>
+        <v>543380</v>
       </c>
       <c r="R11" t="n">
-        <v>7204278</v>
+        <v>7204272</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210223</v>
+        <v>113210196</v>
       </c>
       <c r="B12" t="n">
-        <v>79156</v>
+        <v>56773</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,38 +1817,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543414</v>
+        <v>543372</v>
       </c>
       <c r="R12" t="n">
-        <v>7204395</v>
+        <v>7204028</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210262</v>
+        <v>113210274</v>
       </c>
       <c r="B13" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543464</v>
+        <v>543417</v>
       </c>
       <c r="R13" t="n">
-        <v>7203981</v>
+        <v>7204383</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210261</v>
+        <v>113210222</v>
       </c>
       <c r="B14" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543502</v>
+        <v>543338</v>
       </c>
       <c r="R14" t="n">
-        <v>7203971</v>
+        <v>7204158</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210270</v>
+        <v>113210188</v>
       </c>
       <c r="B15" t="n">
-        <v>78158</v>
+        <v>74345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543369</v>
+        <v>543416</v>
       </c>
       <c r="R15" t="n">
-        <v>7204270</v>
+        <v>7204379</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210275</v>
+        <v>113210273</v>
       </c>
       <c r="B16" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543411</v>
+        <v>543426</v>
       </c>
       <c r="R16" t="n">
-        <v>7204394</v>
+        <v>7204339</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210269</v>
+        <v>113210220</v>
       </c>
       <c r="B17" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543356</v>
+        <v>543501</v>
       </c>
       <c r="R17" t="n">
-        <v>7204196</v>
+        <v>7203965</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210265</v>
+        <v>113210259</v>
       </c>
       <c r="B18" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543457</v>
+        <v>543507</v>
       </c>
       <c r="R18" t="n">
-        <v>7204023</v>
+        <v>7203943</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210186</v>
+        <v>113210219</v>
       </c>
       <c r="B19" t="n">
-        <v>74339</v>
+        <v>79229</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543457</v>
+        <v>543507</v>
       </c>
       <c r="R19" t="n">
-        <v>7204024</v>
+        <v>7203943</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210274</v>
+        <v>113210194</v>
       </c>
       <c r="B20" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,34 +2722,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543417</v>
+        <v>543464</v>
       </c>
       <c r="R20" t="n">
-        <v>7204383</v>
+        <v>7204006</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210267</v>
+        <v>113210198</v>
       </c>
       <c r="B21" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,34 +2839,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543370</v>
+        <v>543348</v>
       </c>
       <c r="R21" t="n">
-        <v>7204023</v>
+        <v>7204165</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2893,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210195</v>
+        <v>113210221</v>
       </c>
       <c r="B22" t="n">
-        <v>56769</v>
+        <v>79229</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,39 +2956,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543458</v>
+        <v>543400</v>
       </c>
       <c r="R22" t="n">
-        <v>7204009</v>
+        <v>7204030</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210187</v>
+        <v>113210277</v>
       </c>
       <c r="B23" t="n">
-        <v>74339</v>
+        <v>78164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3063,21 +3068,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3087,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543382</v>
+        <v>543441</v>
       </c>
       <c r="R23" t="n">
-        <v>7204281</v>
+        <v>7204521</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210277</v>
+        <v>113210269</v>
       </c>
       <c r="B24" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543441</v>
+        <v>543356</v>
       </c>
       <c r="R24" t="n">
-        <v>7204521</v>
+        <v>7204196</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210221</v>
+        <v>113210264</v>
       </c>
       <c r="B25" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,21 +3292,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3311,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543400</v>
+        <v>543460</v>
       </c>
       <c r="R25" t="n">
-        <v>7204030</v>
+        <v>7204008</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3346,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210229</v>
+        <v>113210206</v>
       </c>
       <c r="B26" t="n">
-        <v>79222</v>
+        <v>79255</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3395,25 +3400,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3423,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543341</v>
+        <v>543426</v>
       </c>
       <c r="R26" t="n">
-        <v>7204156</v>
+        <v>7204342</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3458,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210239</v>
+        <v>113210195</v>
       </c>
       <c r="B27" t="n">
-        <v>90101</v>
+        <v>56773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3511,34 +3516,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543380</v>
+        <v>543458</v>
       </c>
       <c r="R27" t="n">
-        <v>7204272</v>
+        <v>7204009</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3570,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,10 +3617,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210232</v>
+        <v>113210265</v>
       </c>
       <c r="B28" t="n">
-        <v>79256</v>
+        <v>78164</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3619,25 +3629,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3647,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543400</v>
+        <v>543457</v>
       </c>
       <c r="R28" t="n">
-        <v>7204030</v>
+        <v>7204023</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3682,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,10 +3729,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210266</v>
+        <v>113210272</v>
       </c>
       <c r="B29" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3759,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543399</v>
+        <v>543381</v>
       </c>
       <c r="R29" t="n">
-        <v>7204037</v>
+        <v>7204285</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3794,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210193</v>
+        <v>113210263</v>
       </c>
       <c r="B30" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3847,39 +3857,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543467</v>
+        <v>543461</v>
       </c>
       <c r="R30" t="n">
-        <v>7203980</v>
+        <v>7204010</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3911,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3921,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210194</v>
+        <v>113210232</v>
       </c>
       <c r="B31" t="n">
-        <v>56769</v>
+        <v>79262</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3960,43 +3965,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543464</v>
+        <v>543400</v>
       </c>
       <c r="R31" t="n">
-        <v>7204006</v>
+        <v>7204030</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210264</v>
+        <v>113210261</v>
       </c>
       <c r="B32" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543460</v>
+        <v>543502</v>
       </c>
       <c r="R32" t="n">
-        <v>7204008</v>
+        <v>7203971</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4177,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113210259</v>
+        <v>113210234</v>
       </c>
       <c r="B33" t="n">
-        <v>78158</v>
+        <v>77145</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4193,21 +4193,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543507</v>
+        <v>543438</v>
       </c>
       <c r="R33" t="n">
-        <v>7203943</v>
+        <v>7204529</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210272</v>
+        <v>113210223</v>
       </c>
       <c r="B34" t="n">
-        <v>78158</v>
+        <v>79162</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4301,25 +4301,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543381</v>
+        <v>543414</v>
       </c>
       <c r="R34" t="n">
-        <v>7204285</v>
+        <v>7204395</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,10 +4401,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210273</v>
+        <v>113210199</v>
       </c>
       <c r="B35" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4417,34 +4417,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543426</v>
+        <v>543356</v>
       </c>
       <c r="R35" t="n">
-        <v>7204339</v>
+        <v>7204193</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4476,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4486,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210199</v>
+        <v>113210186</v>
       </c>
       <c r="B36" t="n">
-        <v>56769</v>
+        <v>74345</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4529,39 +4534,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543356</v>
+        <v>543457</v>
       </c>
       <c r="R36" t="n">
-        <v>7204193</v>
+        <v>7204024</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,10 +4630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210196</v>
+        <v>113210268</v>
       </c>
       <c r="B37" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,39 +4646,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543372</v>
+        <v>543344</v>
       </c>
       <c r="R37" t="n">
-        <v>7204028</v>
+        <v>7204178</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4710,7 +4705,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4720,7 +4715,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4747,10 +4742,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210188</v>
+        <v>113210229</v>
       </c>
       <c r="B38" t="n">
-        <v>74339</v>
+        <v>79228</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4763,21 +4758,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4787,10 +4782,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543416</v>
+        <v>543341</v>
       </c>
       <c r="R38" t="n">
-        <v>7204379</v>
+        <v>7204156</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4822,7 +4817,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4832,7 +4827,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,10 +4854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210234</v>
+        <v>113210193</v>
       </c>
       <c r="B39" t="n">
-        <v>77139</v>
+        <v>56773</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4875,34 +4870,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543438</v>
+        <v>543467</v>
       </c>
       <c r="R39" t="n">
-        <v>7204529</v>
+        <v>7203980</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113210187</v>
+        <v>113210274</v>
       </c>
       <c r="B2" t="n">
-        <v>74345</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543382</v>
+        <v>543417</v>
       </c>
       <c r="R2" t="n">
-        <v>7204281</v>
+        <v>7204383</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113210275</v>
+        <v>113210219</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543411</v>
+        <v>543507</v>
       </c>
       <c r="R3" t="n">
-        <v>7204394</v>
+        <v>7203943</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113210201</v>
+        <v>113210261</v>
       </c>
       <c r="B4" t="n">
-        <v>56773</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543371</v>
+        <v>543502</v>
       </c>
       <c r="R4" t="n">
-        <v>7204278</v>
+        <v>7203971</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113210271</v>
+        <v>113210193</v>
       </c>
       <c r="B5" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543369</v>
+        <v>543467</v>
       </c>
       <c r="R5" t="n">
-        <v>7204284</v>
+        <v>7203980</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113210267</v>
+        <v>113210206</v>
       </c>
       <c r="B6" t="n">
-        <v>78164</v>
+        <v>79255</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543370</v>
+        <v>543426</v>
       </c>
       <c r="R6" t="n">
-        <v>7204023</v>
+        <v>7204342</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113210266</v>
+        <v>113210221</v>
       </c>
       <c r="B7" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543399</v>
+        <v>543400</v>
       </c>
       <c r="R7" t="n">
-        <v>7204037</v>
+        <v>7204030</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113210262</v>
+        <v>113210199</v>
       </c>
       <c r="B8" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543464</v>
+        <v>543356</v>
       </c>
       <c r="R8" t="n">
-        <v>7203981</v>
+        <v>7204193</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113210200</v>
+        <v>113210201</v>
       </c>
       <c r="B9" t="n">
         <v>56773</v>
@@ -1509,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543369</v>
+        <v>543371</v>
       </c>
       <c r="R9" t="n">
-        <v>7204270</v>
+        <v>7204278</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113210270</v>
+        <v>113210194</v>
       </c>
       <c r="B10" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1602,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543369</v>
+        <v>543464</v>
       </c>
       <c r="R10" t="n">
-        <v>7204270</v>
+        <v>7204006</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113210196</v>
+        <v>113210268</v>
       </c>
       <c r="B12" t="n">
-        <v>56773</v>
+        <v>78164</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543372</v>
+        <v>543344</v>
       </c>
       <c r="R12" t="n">
-        <v>7204028</v>
+        <v>7204178</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1927,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113210274</v>
+        <v>113210266</v>
       </c>
       <c r="B13" t="n">
         <v>78164</v>
@@ -1962,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543417</v>
+        <v>543399</v>
       </c>
       <c r="R13" t="n">
-        <v>7204383</v>
+        <v>7204037</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113210222</v>
+        <v>113210271</v>
       </c>
       <c r="B14" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,21 +2055,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543338</v>
+        <v>543369</v>
       </c>
       <c r="R14" t="n">
-        <v>7204158</v>
+        <v>7204284</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113210188</v>
+        <v>113210265</v>
       </c>
       <c r="B15" t="n">
-        <v>74345</v>
+        <v>78164</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543416</v>
+        <v>543457</v>
       </c>
       <c r="R15" t="n">
-        <v>7204379</v>
+        <v>7204023</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113210273</v>
+        <v>113210198</v>
       </c>
       <c r="B16" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,34 +2279,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543426</v>
+        <v>543348</v>
       </c>
       <c r="R16" t="n">
-        <v>7204339</v>
+        <v>7204165</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113210220</v>
+        <v>113210269</v>
       </c>
       <c r="B17" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,21 +2396,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543501</v>
+        <v>543356</v>
       </c>
       <c r="R17" t="n">
-        <v>7203965</v>
+        <v>7204196</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,7 +2492,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113210259</v>
+        <v>113210277</v>
       </c>
       <c r="B18" t="n">
         <v>78164</v>
@@ -2522,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543507</v>
+        <v>543441</v>
       </c>
       <c r="R18" t="n">
-        <v>7203943</v>
+        <v>7204521</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113210219</v>
+        <v>113210270</v>
       </c>
       <c r="B19" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543507</v>
+        <v>543369</v>
       </c>
       <c r="R19" t="n">
-        <v>7203943</v>
+        <v>7204270</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113210194</v>
+        <v>113210223</v>
       </c>
       <c r="B20" t="n">
-        <v>56773</v>
+        <v>79162</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,43 +2728,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543464</v>
+        <v>543414</v>
       </c>
       <c r="R20" t="n">
-        <v>7204006</v>
+        <v>7204395</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2786,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113210198</v>
+        <v>113210259</v>
       </c>
       <c r="B21" t="n">
-        <v>56773</v>
+        <v>78164</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,39 +2844,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543348</v>
+        <v>543507</v>
       </c>
       <c r="R21" t="n">
-        <v>7204165</v>
+        <v>7203943</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113210221</v>
+        <v>113210272</v>
       </c>
       <c r="B22" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543400</v>
+        <v>543381</v>
       </c>
       <c r="R22" t="n">
-        <v>7204030</v>
+        <v>7204285</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,7 +3052,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113210277</v>
+        <v>113210275</v>
       </c>
       <c r="B23" t="n">
         <v>78164</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543441</v>
+        <v>543411</v>
       </c>
       <c r="R23" t="n">
-        <v>7204521</v>
+        <v>7204394</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113210269</v>
+        <v>113210220</v>
       </c>
       <c r="B24" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543356</v>
+        <v>543501</v>
       </c>
       <c r="R24" t="n">
-        <v>7204196</v>
+        <v>7203965</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113210264</v>
+        <v>113210195</v>
       </c>
       <c r="B25" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,34 +3292,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543460</v>
+        <v>543458</v>
       </c>
       <c r="R25" t="n">
-        <v>7204008</v>
+        <v>7204009</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3388,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113210206</v>
+        <v>113210200</v>
       </c>
       <c r="B26" t="n">
-        <v>79255</v>
+        <v>56773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,38 +3405,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543426</v>
+        <v>543369</v>
       </c>
       <c r="R26" t="n">
-        <v>7204342</v>
+        <v>7204270</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3463,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113210195</v>
+        <v>113210187</v>
       </c>
       <c r="B27" t="n">
-        <v>56773</v>
+        <v>74345</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3516,39 +3526,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543458</v>
+        <v>543382</v>
       </c>
       <c r="R27" t="n">
-        <v>7204009</v>
+        <v>7204281</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3580,7 +3585,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3595,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,7 +3622,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113210265</v>
+        <v>113210264</v>
       </c>
       <c r="B28" t="n">
         <v>78164</v>
@@ -3657,10 +3662,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543457</v>
+        <v>543460</v>
       </c>
       <c r="R28" t="n">
-        <v>7204023</v>
+        <v>7204008</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3692,7 +3697,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3707,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,7 +3734,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113210272</v>
+        <v>113210267</v>
       </c>
       <c r="B29" t="n">
         <v>78164</v>
@@ -3769,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543381</v>
+        <v>543370</v>
       </c>
       <c r="R29" t="n">
-        <v>7204285</v>
+        <v>7204023</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,7 +3809,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3819,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,7 +3846,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113210263</v>
+        <v>113210262</v>
       </c>
       <c r="B30" t="n">
         <v>78164</v>
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543461</v>
+        <v>543464</v>
       </c>
       <c r="R30" t="n">
-        <v>7204010</v>
+        <v>7203981</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3916,7 +3921,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3931,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113210232</v>
+        <v>113210273</v>
       </c>
       <c r="B31" t="n">
-        <v>79262</v>
+        <v>78164</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3965,25 +3970,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543400</v>
+        <v>543426</v>
       </c>
       <c r="R31" t="n">
-        <v>7204030</v>
+        <v>7204339</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4028,7 +4033,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4043,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,7 +4070,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113210261</v>
+        <v>113210263</v>
       </c>
       <c r="B32" t="n">
         <v>78164</v>
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543502</v>
+        <v>543461</v>
       </c>
       <c r="R32" t="n">
-        <v>7203971</v>
+        <v>7204010</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4140,7 +4145,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4155,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4289,10 +4294,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113210223</v>
+        <v>113210186</v>
       </c>
       <c r="B34" t="n">
-        <v>79162</v>
+        <v>74345</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4301,25 +4306,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4329,10 +4334,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543414</v>
+        <v>543457</v>
       </c>
       <c r="R34" t="n">
-        <v>7204395</v>
+        <v>7204024</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4364,7 +4369,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4374,7 +4379,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,10 +4406,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113210199</v>
+        <v>113210232</v>
       </c>
       <c r="B35" t="n">
-        <v>56773</v>
+        <v>79262</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4413,43 +4418,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543356</v>
+        <v>543400</v>
       </c>
       <c r="R35" t="n">
-        <v>7204193</v>
+        <v>7204030</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,7 +4518,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113210186</v>
+        <v>113210188</v>
       </c>
       <c r="B36" t="n">
         <v>74345</v>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543457</v>
+        <v>543416</v>
       </c>
       <c r="R36" t="n">
-        <v>7204024</v>
+        <v>7204379</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,10 +4630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113210268</v>
+        <v>113210196</v>
       </c>
       <c r="B37" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,34 +4646,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543344</v>
+        <v>543372</v>
       </c>
       <c r="R37" t="n">
-        <v>7204178</v>
+        <v>7204028</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4705,7 +4710,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4715,7 +4720,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4742,10 +4747,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113210229</v>
+        <v>113210222</v>
       </c>
       <c r="B38" t="n">
-        <v>79228</v>
+        <v>79229</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4758,21 +4763,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4782,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543341</v>
+        <v>543338</v>
       </c>
       <c r="R38" t="n">
-        <v>7204156</v>
+        <v>7204158</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4854,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113210193</v>
+        <v>113210229</v>
       </c>
       <c r="B39" t="n">
-        <v>56773</v>
+        <v>79228</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4870,39 +4875,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tummen, Stalon, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543467</v>
+        <v>543341</v>
       </c>
       <c r="R39" t="n">
-        <v>7203980</v>
+        <v>7204156</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 48183-2023 artfynd.xlsx
+++ b/artfynd/A 48183-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
